--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654DB91F-BE5A-6541-8081-5EB5D9F0AA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967CEE91-4A6A-B042-8A30-EFFC41F0BA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25520" yWindow="-18700" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>No.22</t>
+  </si>
+  <si>
+    <t>axle crown</t>
+  </si>
+  <si>
+    <t>fork offset</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1156,9 @@
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="C21" s="3">
         <v>430</v>
       </c>
@@ -1178,7 +1186,9 @@
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="C22" s="5">
         <v>47</v>
       </c>

--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967CEE91-4A6A-B042-8A30-EFFC41F0BA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682BB096-D8F9-0E48-9732-80FC3E2D84F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -1572,9 +1572,7 @@
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="3"/>

--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682BB096-D8F9-0E48-9732-80FC3E2D84F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1226D6-C381-8F4B-9101-07455AD7B17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,13 +354,16 @@
   </si>
   <si>
     <t>fork offset</t>
+  </si>
+  <si>
+    <t>https://22bicycles.com/cdn/shop/files/No._22_Drifter_Charcoal_Green_Green.jpg?v=1705360564&amp;width=750</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -392,6 +395,13 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -410,18 +420,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -762,6 +775,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
@@ -2015,6 +2033,9 @@
       <c r="J72" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{B965218A-A1BC-8947-A5EB-DB9AE4001A87}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1226D6-C381-8F4B-9101-07455AD7B17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB77A65B-6A37-7C4A-8007-7408AC332C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13000" yWindow="980" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>a8:i32</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -357,6 +354,15 @@
   </si>
   <si>
     <t>https://22bicycles.com/cdn/shop/files/No._22_Drifter_Charcoal_Green_Green.jpg?v=1705360564&amp;width=750</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Johnstown, New York, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -740,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -748,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,12 +778,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -801,28 +807,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -831,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="1">
         <v>515</v>
@@ -861,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1">
         <v>420</v>
@@ -891,7 +897,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1">
         <v>100</v>
@@ -921,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1">
         <v>75.5</v>
@@ -951,7 +957,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="1">
         <v>69.5</v>
@@ -981,7 +987,7 @@
         <v>76</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="1">
         <v>602</v>
@@ -1011,7 +1017,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="1">
         <v>440</v>
@@ -1041,7 +1047,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="1">
         <v>83</v>
@@ -1071,7 +1077,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="1">
         <v>366</v>
@@ -1101,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="1">
         <v>565</v>
@@ -1131,7 +1137,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="1">
         <v>770</v>
@@ -1175,7 +1181,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="3">
         <v>430</v>
@@ -1205,7 +1211,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" s="5">
         <v>47</v>
@@ -1665,7 +1671,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -1711,7 +1717,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -1743,7 +1749,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -1893,7 +1899,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -1941,7 +1947,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -1957,7 +1963,7 @@
         <v>63</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2021,7 +2027,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2032,6 +2038,14 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>107</v>
+      </c>
+      <c r="B73" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{B965218A-A1BC-8947-A5EB-DB9AE4001A87}"/>

--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB77A65B-6A37-7C4A-8007-7408AC332C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CA5B8D-5C45-424B-97B7-F1A064E54B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13000" yWindow="980" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -735,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1668,11 +1686,9 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>78</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1684,7 +1700,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1698,11 +1714,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1">
-        <v>27.2</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1714,11 +1728,9 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1730,11 +1742,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="1">
-        <v>46</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1746,11 +1756,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1762,10 +1770,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="1">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -1778,11 +1786,9 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="1">
-        <v>160</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1794,9 +1800,11 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1808,10 +1816,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -1824,9 +1832,11 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46</v>
+      </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1838,9 +1848,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1852,9 +1864,11 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B61" s="1">
+        <v>160</v>
+      </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -1866,10 +1880,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -1882,7 +1896,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1896,10 +1910,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -1912,11 +1926,9 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -1928,11 +1940,9 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -1944,11 +1954,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>102</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -1960,10 +1968,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -1976,11 +1984,9 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69" s="1">
-        <v>6199</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -1992,10 +1998,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="1">
-        <v>11811</v>
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -2008,7 +2014,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>74</v>
@@ -2024,10 +2030,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2039,10 +2045,106 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6199</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1">
+        <v>11811</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>107</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>108</v>
       </c>
     </row>

--- a/data/gravel/No22 Drifter 2025.xlsx
+++ b/data/gravel/No22 Drifter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CA5B8D-5C45-424B-97B7-F1A064E54B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660C27E0-154C-C748-BEDE-42B993757807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -1928,7 +1928,9 @@
       <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
